--- a/AI教育培训SaaS平台需求清单/乌兹别克教育 APP-需求功能清单_通俗版.xlsx
+++ b/AI教育培训SaaS平台需求清单/乌兹别克教育 APP-需求功能清单_通俗版.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32460" windowHeight="16660"/>
+    <workbookView windowWidth="26860" windowHeight="13700"/>
   </bookViews>
   <sheets>
     <sheet name="通俗版需求" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">通俗版需求!$A$1:$E$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">通俗版需求!$A$1:$E$318</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="710">
   <si>
     <t>端口</t>
   </si>
@@ -216,12 +216,6 @@
   </si>
   <si>
     <t>下载课件、演示文稿、习题包</t>
-  </si>
-  <si>
-    <t>多语字幕开关</t>
-  </si>
-  <si>
-    <t>录播 / 回放可切换 俄/乌/英/中 字幕</t>
   </si>
   <si>
     <t>学习管理</t>
@@ -2168,18 +2162,6 @@
   </si>
   <si>
     <t>未成年专项保护</t>
-  </si>
-  <si>
-    <t>苹果「应用追踪透明度」提示</t>
-  </si>
-  <si>
-    <t>苹果 iOS14 及以上：首次须按系统弹出「是否允许广告追踪」询问（行业常用缩写 ATT）</t>
-  </si>
-  <si>
-    <t>iOS 苹果隐私清单</t>
-  </si>
-  <si>
-    <t>iOS 17+ 隐私清单 苹果隐私配置文件</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2174,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2210,13 +2192,6 @@
       <sz val="12"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2363,7 +2338,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2397,12 +2372,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2736,28 +2705,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2766,37 +2738,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2811,77 +2783,74 @@
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2916,17 +2885,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3274,7 +3234,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E318"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="18.4230769230769" customWidth="1"/>
@@ -3448,7 +3408,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" ht="36" spans="1:5">
+    <row r="13" ht="18" spans="1:5">
       <c r="A13" s="5"/>
       <c r="B13" s="2" t="s">
         <v>30</v>
@@ -3649,12 +3609,14 @@
     </row>
     <row r="28" ht="18" spans="1:5">
       <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
+      <c r="B28" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>9</v>
@@ -3662,9 +3624,7 @@
     </row>
     <row r="29" ht="18" spans="1:5">
       <c r="A29" s="5"/>
-      <c r="B29" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="B29" s="5"/>
       <c r="C29" s="3" t="s">
         <v>65</v>
       </c>
@@ -3755,7 +3715,7 @@
     </row>
     <row r="36" ht="18" spans="1:5">
       <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
+      <c r="B36" s="6"/>
       <c r="C36" s="3" t="s">
         <v>79</v>
       </c>
@@ -3768,12 +3728,14 @@
     </row>
     <row r="37" ht="18" spans="1:5">
       <c r="A37" s="5"/>
-      <c r="B37" s="6"/>
+      <c r="B37" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="C37" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>9</v>
@@ -3781,9 +3743,7 @@
     </row>
     <row r="38" ht="18" spans="1:5">
       <c r="A38" s="5"/>
-      <c r="B38" s="2" t="s">
-        <v>83</v>
-      </c>
+      <c r="B38" s="5"/>
       <c r="C38" s="3" t="s">
         <v>84</v>
       </c>
@@ -3874,7 +3834,7 @@
     </row>
     <row r="45" ht="18" spans="1:5">
       <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="3" t="s">
         <v>98</v>
       </c>
@@ -3887,12 +3847,14 @@
     </row>
     <row r="46" ht="18" spans="1:5">
       <c r="A46" s="5"/>
-      <c r="B46" s="6"/>
+      <c r="B46" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="C46" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>9</v>
@@ -3900,9 +3862,7 @@
     </row>
     <row r="47" ht="18" spans="1:5">
       <c r="A47" s="5"/>
-      <c r="B47" s="2" t="s">
-        <v>102</v>
-      </c>
+      <c r="B47" s="5"/>
       <c r="C47" s="3" t="s">
         <v>103</v>
       </c>
@@ -3980,7 +3940,7 @@
     </row>
     <row r="53" ht="18" spans="1:5">
       <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
+      <c r="B53" s="6"/>
       <c r="C53" s="3" t="s">
         <v>115</v>
       </c>
@@ -3993,12 +3953,14 @@
     </row>
     <row r="54" ht="18" spans="1:5">
       <c r="A54" s="5"/>
-      <c r="B54" s="6"/>
+      <c r="B54" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="C54" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>9</v>
@@ -4006,9 +3968,7 @@
     </row>
     <row r="55" ht="18" spans="1:5">
       <c r="A55" s="5"/>
-      <c r="B55" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="B55" s="5"/>
       <c r="C55" s="3" t="s">
         <v>120</v>
       </c>
@@ -4060,7 +4020,7 @@
     </row>
     <row r="59" ht="18" spans="1:5">
       <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
+      <c r="B59" s="6"/>
       <c r="C59" s="3" t="s">
         <v>128</v>
       </c>
@@ -4073,12 +4033,14 @@
     </row>
     <row r="60" ht="18" spans="1:5">
       <c r="A60" s="5"/>
-      <c r="B60" s="6"/>
+      <c r="B60" s="2" t="s">
+        <v>130</v>
+      </c>
       <c r="C60" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>9</v>
@@ -4086,9 +4048,7 @@
     </row>
     <row r="61" ht="18" spans="1:5">
       <c r="A61" s="5"/>
-      <c r="B61" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="B61" s="5"/>
       <c r="C61" s="3" t="s">
         <v>133</v>
       </c>
@@ -4127,7 +4087,7 @@
     </row>
     <row r="64" ht="18" spans="1:5">
       <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
+      <c r="B64" s="6"/>
       <c r="C64" s="3" t="s">
         <v>139</v>
       </c>
@@ -4140,12 +4100,14 @@
     </row>
     <row r="65" ht="18" spans="1:5">
       <c r="A65" s="5"/>
-      <c r="B65" s="6"/>
+      <c r="B65" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="C65" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>9</v>
@@ -4153,9 +4115,7 @@
     </row>
     <row r="66" ht="18" spans="1:5">
       <c r="A66" s="5"/>
-      <c r="B66" s="2" t="s">
-        <v>143</v>
-      </c>
+      <c r="B66" s="5"/>
       <c r="C66" s="3" t="s">
         <v>144</v>
       </c>
@@ -4246,7 +4206,7 @@
     </row>
     <row r="73" ht="18" spans="1:5">
       <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
+      <c r="B73" s="6"/>
       <c r="C73" s="3" t="s">
         <v>158</v>
       </c>
@@ -4259,12 +4219,14 @@
     </row>
     <row r="74" ht="18" spans="1:5">
       <c r="A74" s="5"/>
-      <c r="B74" s="6"/>
+      <c r="B74" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="C74" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>9</v>
@@ -4272,9 +4234,7 @@
     </row>
     <row r="75" ht="18" spans="1:5">
       <c r="A75" s="5"/>
-      <c r="B75" s="2" t="s">
-        <v>162</v>
-      </c>
+      <c r="B75" s="5"/>
       <c r="C75" s="3" t="s">
         <v>163</v>
       </c>
@@ -4298,9 +4258,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" ht="36" spans="1:5">
+    <row r="77" ht="18" spans="1:5">
       <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
+      <c r="B77" s="6"/>
       <c r="C77" s="3" t="s">
         <v>167</v>
       </c>
@@ -4313,12 +4273,14 @@
     </row>
     <row r="78" ht="18" spans="1:5">
       <c r="A78" s="5"/>
-      <c r="B78" s="6"/>
+      <c r="B78" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="C78" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>9</v>
@@ -4326,9 +4288,7 @@
     </row>
     <row r="79" ht="18" spans="1:5">
       <c r="A79" s="5"/>
-      <c r="B79" s="2" t="s">
-        <v>171</v>
-      </c>
+      <c r="B79" s="5"/>
       <c r="C79" s="3" t="s">
         <v>172</v>
       </c>
@@ -4367,7 +4327,7 @@
     </row>
     <row r="82" ht="18" spans="1:5">
       <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
+      <c r="B82" s="6"/>
       <c r="C82" s="3" t="s">
         <v>178</v>
       </c>
@@ -4380,12 +4340,14 @@
     </row>
     <row r="83" ht="18" spans="1:5">
       <c r="A83" s="5"/>
-      <c r="B83" s="6"/>
+      <c r="B83" s="2" t="s">
+        <v>180</v>
+      </c>
       <c r="C83" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>9</v>
@@ -4393,9 +4355,7 @@
     </row>
     <row r="84" ht="18" spans="1:5">
       <c r="A84" s="5"/>
-      <c r="B84" s="2" t="s">
-        <v>182</v>
-      </c>
+      <c r="B84" s="5"/>
       <c r="C84" s="3" t="s">
         <v>183</v>
       </c>
@@ -4421,7 +4381,7 @@
     </row>
     <row r="86" ht="18" spans="1:5">
       <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
+      <c r="B86" s="6"/>
       <c r="C86" s="3" t="s">
         <v>187</v>
       </c>
@@ -4432,24 +4392,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" ht="18" spans="1:5">
+    <row r="87" ht="36" spans="1:5">
       <c r="A87" s="5"/>
-      <c r="B87" s="6"/>
+      <c r="B87" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="C87" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" ht="36" spans="1:5">
+    <row r="88" ht="18" spans="1:5">
       <c r="A88" s="5"/>
-      <c r="B88" s="2" t="s">
-        <v>191</v>
-      </c>
+      <c r="B88" s="5"/>
       <c r="C88" s="3" t="s">
         <v>192</v>
       </c>
@@ -4486,7 +4446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" ht="36" spans="1:5">
+    <row r="91" ht="18" spans="1:5">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="3" t="s">
@@ -4501,12 +4461,14 @@
     </row>
     <row r="92" ht="18" spans="1:5">
       <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
+      <c r="B92" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="C92" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>9</v>
@@ -4514,9 +4476,7 @@
     </row>
     <row r="93" ht="18" spans="1:5">
       <c r="A93" s="5"/>
-      <c r="B93" s="2" t="s">
-        <v>202</v>
-      </c>
+      <c r="B93" s="5"/>
       <c r="C93" s="3" t="s">
         <v>203</v>
       </c>
@@ -4566,9 +4526,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" ht="18" spans="1:5">
-      <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
+    <row r="97" ht="53" spans="1:5">
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
       <c r="C97" s="3" t="s">
         <v>211</v>
       </c>
@@ -4579,26 +4539,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" ht="53" spans="1:5">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="3" t="s">
+    <row r="98" ht="18" spans="1:5">
+      <c r="A98" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="B98" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="E98" s="4" t="s">
+      <c r="C98" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="E98" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="99" ht="18" spans="1:5">
-      <c r="A99" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>216</v>
-      </c>
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
       <c r="C99" s="8" t="s">
         <v>217</v>
       </c>
@@ -4635,9 +4595,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" ht="18" spans="1:5">
+    <row r="102" ht="36" spans="1:5">
       <c r="A102" s="10"/>
-      <c r="B102" s="10"/>
+      <c r="B102" s="11"/>
       <c r="C102" s="8" t="s">
         <v>223</v>
       </c>
@@ -4648,14 +4608,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" ht="36" spans="1:5">
+    <row r="103" ht="18" spans="1:5">
       <c r="A103" s="10"/>
-      <c r="B103" s="11"/>
+      <c r="B103" s="7" t="s">
+        <v>225</v>
+      </c>
       <c r="C103" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>9</v>
@@ -4663,9 +4625,7 @@
     </row>
     <row r="104" ht="18" spans="1:5">
       <c r="A104" s="10"/>
-      <c r="B104" s="7" t="s">
-        <v>227</v>
-      </c>
+      <c r="B104" s="10"/>
       <c r="C104" s="8" t="s">
         <v>228</v>
       </c>
@@ -4691,7 +4651,7 @@
     </row>
     <row r="106" ht="18" spans="1:5">
       <c r="A106" s="10"/>
-      <c r="B106" s="10"/>
+      <c r="B106" s="11"/>
       <c r="C106" s="8" t="s">
         <v>232</v>
       </c>
@@ -4704,12 +4664,14 @@
     </row>
     <row r="107" ht="18" spans="1:5">
       <c r="A107" s="10"/>
-      <c r="B107" s="11"/>
+      <c r="B107" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="C107" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>9</v>
@@ -4717,14 +4679,12 @@
     </row>
     <row r="108" ht="18" spans="1:5">
       <c r="A108" s="10"/>
-      <c r="B108" s="7" t="s">
-        <v>236</v>
-      </c>
+      <c r="B108" s="10"/>
       <c r="C108" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>238</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>9</v>
@@ -4732,9 +4692,9 @@
     </row>
     <row r="109" ht="18" spans="1:5">
       <c r="A109" s="10"/>
-      <c r="B109" s="10"/>
+      <c r="B109" s="11"/>
       <c r="C109" s="8" t="s">
-        <v>107</v>
+        <v>238</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>239</v>
@@ -4745,12 +4705,14 @@
     </row>
     <row r="110" ht="18" spans="1:5">
       <c r="A110" s="10"/>
-      <c r="B110" s="11"/>
+      <c r="B110" s="7" t="s">
+        <v>240</v>
+      </c>
       <c r="C110" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>9</v>
@@ -4758,9 +4720,7 @@
     </row>
     <row r="111" ht="18" spans="1:5">
       <c r="A111" s="10"/>
-      <c r="B111" s="7" t="s">
-        <v>242</v>
-      </c>
+      <c r="B111" s="11"/>
       <c r="C111" s="8" t="s">
         <v>243</v>
       </c>
@@ -4773,12 +4733,14 @@
     </row>
     <row r="112" ht="18" spans="1:5">
       <c r="A112" s="10"/>
-      <c r="B112" s="11"/>
+      <c r="B112" s="7" t="s">
+        <v>245</v>
+      </c>
       <c r="C112" s="8" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>9</v>
@@ -4786,9 +4748,7 @@
     </row>
     <row r="113" ht="18" spans="1:5">
       <c r="A113" s="10"/>
-      <c r="B113" s="7" t="s">
-        <v>247</v>
-      </c>
+      <c r="B113" s="11"/>
       <c r="C113" s="8" t="s">
         <v>248</v>
       </c>
@@ -4801,22 +4761,22 @@
     </row>
     <row r="114" ht="18" spans="1:5">
       <c r="A114" s="10"/>
-      <c r="B114" s="11"/>
+      <c r="B114" s="7" t="s">
+        <v>250</v>
+      </c>
       <c r="C114" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="115" ht="18" spans="1:5">
-      <c r="A115" s="10"/>
-      <c r="B115" s="7" t="s">
-        <v>252</v>
-      </c>
+      <c r="A115" s="11"/>
+      <c r="B115" s="11"/>
       <c r="C115" s="8" t="s">
         <v>253</v>
       </c>
@@ -4828,25 +4788,25 @@
       </c>
     </row>
     <row r="116" ht="18" spans="1:5">
-      <c r="A116" s="11"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="8" t="s">
+      <c r="A116" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D116" s="8" t="s">
+      <c r="B116" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E116" s="9" t="s">
+      <c r="C116" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="117" ht="18" spans="1:5">
-      <c r="A117" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
       <c r="C117" s="3" t="s">
         <v>259</v>
       </c>
@@ -4885,12 +4845,12 @@
     </row>
     <row r="120" ht="18" spans="1:5">
       <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
+      <c r="B120" s="6"/>
       <c r="C120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>265</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>266</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>9</v>
@@ -4898,12 +4858,14 @@
     </row>
     <row r="121" ht="18" spans="1:5">
       <c r="A121" s="5"/>
-      <c r="B121" s="6"/>
+      <c r="B121" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="C121" s="3" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>9</v>
@@ -4911,9 +4873,7 @@
     </row>
     <row r="122" ht="18" spans="1:5">
       <c r="A122" s="5"/>
-      <c r="B122" s="2" t="s">
-        <v>268</v>
-      </c>
+      <c r="B122" s="5"/>
       <c r="C122" s="3" t="s">
         <v>269</v>
       </c>
@@ -4939,7 +4899,7 @@
     </row>
     <row r="124" ht="18" spans="1:5">
       <c r="A124" s="5"/>
-      <c r="B124" s="5"/>
+      <c r="B124" s="6"/>
       <c r="C124" s="3" t="s">
         <v>273</v>
       </c>
@@ -4952,12 +4912,14 @@
     </row>
     <row r="125" ht="18" spans="1:5">
       <c r="A125" s="5"/>
-      <c r="B125" s="6"/>
+      <c r="B125" s="2" t="s">
+        <v>275</v>
+      </c>
       <c r="C125" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>9</v>
@@ -4965,9 +4927,7 @@
     </row>
     <row r="126" ht="18" spans="1:5">
       <c r="A126" s="5"/>
-      <c r="B126" s="2" t="s">
-        <v>277</v>
-      </c>
+      <c r="B126" s="5"/>
       <c r="C126" s="3" t="s">
         <v>278</v>
       </c>
@@ -5006,7 +4966,7 @@
     </row>
     <row r="129" ht="18" spans="1:5">
       <c r="A129" s="5"/>
-      <c r="B129" s="5"/>
+      <c r="B129" s="6"/>
       <c r="C129" s="3" t="s">
         <v>284</v>
       </c>
@@ -5019,12 +4979,14 @@
     </row>
     <row r="130" ht="18" spans="1:5">
       <c r="A130" s="5"/>
-      <c r="B130" s="6"/>
+      <c r="B130" s="2" t="s">
+        <v>286</v>
+      </c>
       <c r="C130" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>9</v>
@@ -5032,9 +4994,7 @@
     </row>
     <row r="131" ht="18" spans="1:5">
       <c r="A131" s="5"/>
-      <c r="B131" s="2" t="s">
-        <v>288</v>
-      </c>
+      <c r="B131" s="5"/>
       <c r="C131" s="3" t="s">
         <v>289</v>
       </c>
@@ -5060,7 +5020,7 @@
     </row>
     <row r="133" ht="18" spans="1:5">
       <c r="A133" s="5"/>
-      <c r="B133" s="5"/>
+      <c r="B133" s="6"/>
       <c r="C133" s="3" t="s">
         <v>293</v>
       </c>
@@ -5073,12 +5033,14 @@
     </row>
     <row r="134" ht="18" spans="1:5">
       <c r="A134" s="5"/>
-      <c r="B134" s="6"/>
+      <c r="B134" s="2" t="s">
+        <v>295</v>
+      </c>
       <c r="C134" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>9</v>
@@ -5086,9 +5048,7 @@
     </row>
     <row r="135" ht="18" spans="1:5">
       <c r="A135" s="5"/>
-      <c r="B135" s="2" t="s">
-        <v>297</v>
-      </c>
+      <c r="B135" s="5"/>
       <c r="C135" s="3" t="s">
         <v>298</v>
       </c>
@@ -5103,10 +5063,10 @@
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="D136" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>9</v>
@@ -5114,9 +5074,9 @@
     </row>
     <row r="137" ht="18" spans="1:5">
       <c r="A137" s="5"/>
-      <c r="B137" s="5"/>
+      <c r="B137" s="6"/>
       <c r="C137" s="3" t="s">
-        <v>242</v>
+        <v>301</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>302</v>
@@ -5127,12 +5087,14 @@
     </row>
     <row r="138" ht="18" spans="1:5">
       <c r="A138" s="5"/>
-      <c r="B138" s="6"/>
+      <c r="B138" s="2" t="s">
+        <v>303</v>
+      </c>
       <c r="C138" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>9</v>
@@ -5140,9 +5102,7 @@
     </row>
     <row r="139" ht="18" spans="1:5">
       <c r="A139" s="5"/>
-      <c r="B139" s="2" t="s">
-        <v>305</v>
-      </c>
+      <c r="B139" s="5"/>
       <c r="C139" s="3" t="s">
         <v>306</v>
       </c>
@@ -5207,7 +5167,7 @@
     </row>
     <row r="144" ht="18" spans="1:5">
       <c r="A144" s="5"/>
-      <c r="B144" s="5"/>
+      <c r="B144" s="6"/>
       <c r="C144" s="3" t="s">
         <v>316</v>
       </c>
@@ -5220,12 +5180,14 @@
     </row>
     <row r="145" ht="18" spans="1:5">
       <c r="A145" s="5"/>
-      <c r="B145" s="6"/>
+      <c r="B145" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="C145" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E145" s="4" t="s">
         <v>9</v>
@@ -5233,9 +5195,7 @@
     </row>
     <row r="146" ht="18" spans="1:5">
       <c r="A146" s="5"/>
-      <c r="B146" s="2" t="s">
-        <v>320</v>
-      </c>
+      <c r="B146" s="5"/>
       <c r="C146" s="3" t="s">
         <v>321</v>
       </c>
@@ -5250,10 +5210,10 @@
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D147" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>9</v>
@@ -5263,7 +5223,7 @@
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="3" t="s">
-        <v>167</v>
+        <v>324</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>325</v>
@@ -5274,7 +5234,7 @@
     </row>
     <row r="149" ht="18" spans="1:5">
       <c r="A149" s="5"/>
-      <c r="B149" s="5"/>
+      <c r="B149" s="6"/>
       <c r="C149" s="3" t="s">
         <v>326</v>
       </c>
@@ -5287,12 +5247,14 @@
     </row>
     <row r="150" ht="18" spans="1:5">
       <c r="A150" s="5"/>
-      <c r="B150" s="6"/>
+      <c r="B150" s="2" t="s">
+        <v>328</v>
+      </c>
       <c r="C150" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E150" s="4" t="s">
         <v>9</v>
@@ -5300,9 +5262,7 @@
     </row>
     <row r="151" ht="18" spans="1:5">
       <c r="A151" s="5"/>
-      <c r="B151" s="2" t="s">
-        <v>330</v>
-      </c>
+      <c r="B151" s="6"/>
       <c r="C151" s="3" t="s">
         <v>331</v>
       </c>
@@ -5315,12 +5275,14 @@
     </row>
     <row r="152" ht="18" spans="1:5">
       <c r="A152" s="5"/>
-      <c r="B152" s="6"/>
+      <c r="B152" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="C152" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>9</v>
@@ -5328,9 +5290,7 @@
     </row>
     <row r="153" ht="18" spans="1:5">
       <c r="A153" s="5"/>
-      <c r="B153" s="2" t="s">
-        <v>335</v>
-      </c>
+      <c r="B153" s="5"/>
       <c r="C153" s="3" t="s">
         <v>336</v>
       </c>
@@ -5342,8 +5302,8 @@
       </c>
     </row>
     <row r="154" ht="18" spans="1:5">
-      <c r="A154" s="5"/>
-      <c r="B154" s="5"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="6"/>
       <c r="C154" s="3" t="s">
         <v>338</v>
       </c>
@@ -5355,25 +5315,25 @@
       </c>
     </row>
     <row r="155" ht="18" spans="1:5">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="3" t="s">
+      <c r="A155" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="B155" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="C155" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="E155" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="156" ht="18" spans="1:5">
-      <c r="A156" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>343</v>
-      </c>
+      <c r="A156" s="10"/>
+      <c r="B156" s="10"/>
       <c r="C156" s="8" t="s">
         <v>344</v>
       </c>
@@ -5399,7 +5359,7 @@
     </row>
     <row r="158" ht="18" spans="1:5">
       <c r="A158" s="10"/>
-      <c r="B158" s="10"/>
+      <c r="B158" s="11"/>
       <c r="C158" s="8" t="s">
         <v>348</v>
       </c>
@@ -5412,12 +5372,14 @@
     </row>
     <row r="159" ht="18" spans="1:5">
       <c r="A159" s="10"/>
-      <c r="B159" s="11"/>
+      <c r="B159" s="7" t="s">
+        <v>350</v>
+      </c>
       <c r="C159" s="8" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D159" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>9</v>
@@ -5425,9 +5387,7 @@
     </row>
     <row r="160" ht="18" spans="1:5">
       <c r="A160" s="10"/>
-      <c r="B160" s="7" t="s">
-        <v>352</v>
-      </c>
+      <c r="B160" s="10"/>
       <c r="C160" s="8" t="s">
         <v>353</v>
       </c>
@@ -5466,7 +5426,7 @@
     </row>
     <row r="163" ht="18" spans="1:5">
       <c r="A163" s="10"/>
-      <c r="B163" s="10"/>
+      <c r="B163" s="11"/>
       <c r="C163" s="8" t="s">
         <v>359</v>
       </c>
@@ -5479,12 +5439,14 @@
     </row>
     <row r="164" ht="18" spans="1:5">
       <c r="A164" s="10"/>
-      <c r="B164" s="11"/>
+      <c r="B164" s="7" t="s">
+        <v>361</v>
+      </c>
       <c r="C164" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D164" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>9</v>
@@ -5492,9 +5454,7 @@
     </row>
     <row r="165" ht="18" spans="1:5">
       <c r="A165" s="10"/>
-      <c r="B165" s="7" t="s">
-        <v>363</v>
-      </c>
+      <c r="B165" s="10"/>
       <c r="C165" s="8" t="s">
         <v>364</v>
       </c>
@@ -5507,7 +5467,7 @@
     </row>
     <row r="166" ht="18" spans="1:5">
       <c r="A166" s="10"/>
-      <c r="B166" s="10"/>
+      <c r="B166" s="11"/>
       <c r="C166" s="8" t="s">
         <v>366</v>
       </c>
@@ -5520,12 +5480,14 @@
     </row>
     <row r="167" ht="18" spans="1:5">
       <c r="A167" s="10"/>
-      <c r="B167" s="11"/>
+      <c r="B167" s="7" t="s">
+        <v>368</v>
+      </c>
       <c r="C167" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>9</v>
@@ -5533,9 +5495,7 @@
     </row>
     <row r="168" ht="18" spans="1:5">
       <c r="A168" s="10"/>
-      <c r="B168" s="7" t="s">
-        <v>370</v>
-      </c>
+      <c r="B168" s="10"/>
       <c r="C168" s="8" t="s">
         <v>371</v>
       </c>
@@ -5546,7 +5506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" ht="18" spans="1:5">
+    <row r="169" ht="36" spans="1:5">
       <c r="A169" s="10"/>
       <c r="B169" s="10"/>
       <c r="C169" s="8" t="s">
@@ -5559,9 +5519,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" ht="36" spans="1:5">
+    <row r="170" ht="18" spans="1:5">
       <c r="A170" s="10"/>
-      <c r="B170" s="10"/>
+      <c r="B170" s="11"/>
       <c r="C170" s="8" t="s">
         <v>375</v>
       </c>
@@ -5574,12 +5534,14 @@
     </row>
     <row r="171" ht="18" spans="1:5">
       <c r="A171" s="10"/>
-      <c r="B171" s="11"/>
+      <c r="B171" s="7" t="s">
+        <v>377</v>
+      </c>
       <c r="C171" s="8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>9</v>
@@ -5587,9 +5549,7 @@
     </row>
     <row r="172" ht="18" spans="1:5">
       <c r="A172" s="10"/>
-      <c r="B172" s="7" t="s">
-        <v>379</v>
-      </c>
+      <c r="B172" s="10"/>
       <c r="C172" s="8" t="s">
         <v>380</v>
       </c>
@@ -5602,7 +5562,7 @@
     </row>
     <row r="173" ht="18" spans="1:5">
       <c r="A173" s="10"/>
-      <c r="B173" s="10"/>
+      <c r="B173" s="11"/>
       <c r="C173" s="8" t="s">
         <v>382</v>
       </c>
@@ -5615,12 +5575,14 @@
     </row>
     <row r="174" ht="18" spans="1:5">
       <c r="A174" s="10"/>
-      <c r="B174" s="11"/>
+      <c r="B174" s="7" t="s">
+        <v>384</v>
+      </c>
       <c r="C174" s="8" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E174" s="9" t="s">
         <v>9</v>
@@ -5628,9 +5590,7 @@
     </row>
     <row r="175" ht="18" spans="1:5">
       <c r="A175" s="10"/>
-      <c r="B175" s="7" t="s">
-        <v>386</v>
-      </c>
+      <c r="B175" s="10"/>
       <c r="C175" s="8" t="s">
         <v>387</v>
       </c>
@@ -5643,7 +5603,7 @@
     </row>
     <row r="176" ht="18" spans="1:5">
       <c r="A176" s="10"/>
-      <c r="B176" s="10"/>
+      <c r="B176" s="11"/>
       <c r="C176" s="8" t="s">
         <v>389</v>
       </c>
@@ -5656,12 +5616,14 @@
     </row>
     <row r="177" ht="18" spans="1:5">
       <c r="A177" s="10"/>
-      <c r="B177" s="11"/>
+      <c r="B177" s="7" t="s">
+        <v>391</v>
+      </c>
       <c r="C177" s="8" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>9</v>
@@ -5669,9 +5631,7 @@
     </row>
     <row r="178" ht="18" spans="1:5">
       <c r="A178" s="10"/>
-      <c r="B178" s="7" t="s">
-        <v>393</v>
-      </c>
+      <c r="B178" s="10"/>
       <c r="C178" s="8" t="s">
         <v>394</v>
       </c>
@@ -5684,7 +5644,7 @@
     </row>
     <row r="179" ht="18" spans="1:5">
       <c r="A179" s="10"/>
-      <c r="B179" s="10"/>
+      <c r="B179" s="11"/>
       <c r="C179" s="8" t="s">
         <v>396</v>
       </c>
@@ -5697,12 +5657,14 @@
     </row>
     <row r="180" ht="18" spans="1:5">
       <c r="A180" s="10"/>
-      <c r="B180" s="11"/>
+      <c r="B180" s="7" t="s">
+        <v>398</v>
+      </c>
       <c r="C180" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E180" s="9" t="s">
         <v>9</v>
@@ -5710,9 +5672,7 @@
     </row>
     <row r="181" ht="18" spans="1:5">
       <c r="A181" s="10"/>
-      <c r="B181" s="7" t="s">
-        <v>400</v>
-      </c>
+      <c r="B181" s="11"/>
       <c r="C181" s="8" t="s">
         <v>401</v>
       </c>
@@ -5725,12 +5685,14 @@
     </row>
     <row r="182" ht="18" spans="1:5">
       <c r="A182" s="10"/>
-      <c r="B182" s="11"/>
+      <c r="B182" s="7" t="s">
+        <v>403</v>
+      </c>
       <c r="C182" s="8" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E182" s="9" t="s">
         <v>9</v>
@@ -5738,9 +5700,7 @@
     </row>
     <row r="183" ht="18" spans="1:5">
       <c r="A183" s="10"/>
-      <c r="B183" s="7" t="s">
-        <v>405</v>
-      </c>
+      <c r="B183" s="11"/>
       <c r="C183" s="8" t="s">
         <v>406</v>
       </c>
@@ -5753,22 +5713,22 @@
     </row>
     <row r="184" ht="18" spans="1:5">
       <c r="A184" s="10"/>
-      <c r="B184" s="11"/>
+      <c r="B184" s="7" t="s">
+        <v>408</v>
+      </c>
       <c r="C184" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E184" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="185" ht="18" spans="1:5">
-      <c r="A185" s="10"/>
-      <c r="B185" s="7" t="s">
-        <v>410</v>
-      </c>
+      <c r="A185" s="11"/>
+      <c r="B185" s="11"/>
       <c r="C185" s="8" t="s">
         <v>411</v>
       </c>
@@ -5780,25 +5740,25 @@
       </c>
     </row>
     <row r="186" ht="18" spans="1:5">
-      <c r="A186" s="11"/>
-      <c r="B186" s="11"/>
-      <c r="C186" s="8" t="s">
+      <c r="A186" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D186" s="8" t="s">
+      <c r="B186" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="E186" s="9" t="s">
+      <c r="C186" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E186" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="187" ht="18" spans="1:5">
-      <c r="A187" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>416</v>
-      </c>
+      <c r="A187" s="5"/>
+      <c r="B187" s="6"/>
       <c r="C187" s="3" t="s">
         <v>417</v>
       </c>
@@ -5811,12 +5771,14 @@
     </row>
     <row r="188" ht="18" spans="1:5">
       <c r="A188" s="5"/>
-      <c r="B188" s="6"/>
+      <c r="B188" s="2" t="s">
+        <v>419</v>
+      </c>
       <c r="C188" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E188" s="4" t="s">
         <v>9</v>
@@ -5824,9 +5786,7 @@
     </row>
     <row r="189" ht="18" spans="1:5">
       <c r="A189" s="5"/>
-      <c r="B189" s="2" t="s">
-        <v>421</v>
-      </c>
+      <c r="B189" s="5"/>
       <c r="C189" s="3" t="s">
         <v>422</v>
       </c>
@@ -5839,7 +5799,7 @@
     </row>
     <row r="190" ht="18" spans="1:5">
       <c r="A190" s="5"/>
-      <c r="B190" s="5"/>
+      <c r="B190" s="6"/>
       <c r="C190" s="3" t="s">
         <v>424</v>
       </c>
@@ -5852,12 +5812,14 @@
     </row>
     <row r="191" ht="18" spans="1:5">
       <c r="A191" s="5"/>
-      <c r="B191" s="6"/>
+      <c r="B191" s="2" t="s">
+        <v>426</v>
+      </c>
       <c r="C191" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E191" s="4" t="s">
         <v>9</v>
@@ -5865,9 +5827,7 @@
     </row>
     <row r="192" ht="18" spans="1:5">
       <c r="A192" s="5"/>
-      <c r="B192" s="2" t="s">
-        <v>428</v>
-      </c>
+      <c r="B192" s="6"/>
       <c r="C192" s="3" t="s">
         <v>429</v>
       </c>
@@ -5880,12 +5840,14 @@
     </row>
     <row r="193" ht="18" spans="1:5">
       <c r="A193" s="5"/>
-      <c r="B193" s="6"/>
+      <c r="B193" s="3" t="s">
+        <v>431</v>
+      </c>
       <c r="C193" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E193" s="4" t="s">
         <v>9</v>
@@ -5893,14 +5855,14 @@
     </row>
     <row r="194" ht="18" spans="1:5">
       <c r="A194" s="5"/>
-      <c r="B194" s="3" t="s">
-        <v>433</v>
+      <c r="B194" s="2" t="s">
+        <v>434</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E194" s="4" t="s">
         <v>9</v>
@@ -5908,9 +5870,7 @@
     </row>
     <row r="195" ht="18" spans="1:5">
       <c r="A195" s="5"/>
-      <c r="B195" s="2" t="s">
-        <v>436</v>
-      </c>
+      <c r="B195" s="6"/>
       <c r="C195" s="3" t="s">
         <v>437</v>
       </c>
@@ -5923,12 +5883,14 @@
     </row>
     <row r="196" ht="18" spans="1:5">
       <c r="A196" s="5"/>
-      <c r="B196" s="6"/>
+      <c r="B196" s="3" t="s">
+        <v>439</v>
+      </c>
       <c r="C196" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E196" s="4" t="s">
         <v>9</v>
@@ -5936,14 +5898,14 @@
     </row>
     <row r="197" ht="18" spans="1:5">
       <c r="A197" s="5"/>
-      <c r="B197" s="3" t="s">
-        <v>441</v>
+      <c r="B197" s="2" t="s">
+        <v>442</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>9</v>
@@ -5951,9 +5913,7 @@
     </row>
     <row r="198" ht="18" spans="1:5">
       <c r="A198" s="5"/>
-      <c r="B198" s="2" t="s">
-        <v>444</v>
-      </c>
+      <c r="B198" s="5"/>
       <c r="C198" s="3" t="s">
         <v>445</v>
       </c>
@@ -5965,8 +5925,8 @@
       </c>
     </row>
     <row r="199" ht="18" spans="1:5">
-      <c r="A199" s="5"/>
-      <c r="B199" s="5"/>
+      <c r="A199" s="6"/>
+      <c r="B199" s="6"/>
       <c r="C199" s="3" t="s">
         <v>447</v>
       </c>
@@ -5978,25 +5938,25 @@
       </c>
     </row>
     <row r="200" ht="18" spans="1:5">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="3" t="s">
+      <c r="A200" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D200" s="3" t="s">
+      <c r="B200" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="E200" s="4" t="s">
+      <c r="C200" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="E200" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="201" ht="18" spans="1:5">
-      <c r="A201" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>452</v>
-      </c>
+      <c r="A201" s="10"/>
+      <c r="B201" s="10"/>
       <c r="C201" s="8" t="s">
         <v>453</v>
       </c>
@@ -6008,8 +5968,8 @@
       </c>
     </row>
     <row r="202" ht="18" spans="1:5">
-      <c r="A202" s="12"/>
-      <c r="B202" s="10"/>
+      <c r="A202" s="10"/>
+      <c r="B202" s="11"/>
       <c r="C202" s="8" t="s">
         <v>455</v>
       </c>
@@ -6021,23 +5981,23 @@
       </c>
     </row>
     <row r="203" ht="18" spans="1:5">
-      <c r="A203" s="12"/>
-      <c r="B203" s="11"/>
+      <c r="A203" s="10"/>
+      <c r="B203" s="7" t="s">
+        <v>457</v>
+      </c>
       <c r="C203" s="8" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="204" ht="18" spans="1:5">
-      <c r="A204" s="12"/>
-      <c r="B204" s="7" t="s">
-        <v>459</v>
-      </c>
+      <c r="A204" s="10"/>
+      <c r="B204" s="10"/>
       <c r="C204" s="8" t="s">
         <v>460</v>
       </c>
@@ -6048,8 +6008,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" ht="36" spans="1:5">
-      <c r="A205" s="12"/>
+    <row r="205" ht="18" spans="1:5">
+      <c r="A205" s="10"/>
       <c r="B205" s="10"/>
       <c r="C205" s="8" t="s">
         <v>462</v>
@@ -6062,7 +6022,7 @@
       </c>
     </row>
     <row r="206" ht="18" spans="1:5">
-      <c r="A206" s="12"/>
+      <c r="A206" s="10"/>
       <c r="B206" s="10"/>
       <c r="C206" s="8" t="s">
         <v>464</v>
@@ -6075,8 +6035,8 @@
       </c>
     </row>
     <row r="207" ht="18" spans="1:5">
-      <c r="A207" s="12"/>
-      <c r="B207" s="10"/>
+      <c r="A207" s="10"/>
+      <c r="B207" s="11"/>
       <c r="C207" s="8" t="s">
         <v>466</v>
       </c>
@@ -6088,23 +6048,23 @@
       </c>
     </row>
     <row r="208" ht="18" spans="1:5">
-      <c r="A208" s="12"/>
-      <c r="B208" s="11"/>
+      <c r="A208" s="10"/>
+      <c r="B208" s="7" t="s">
+        <v>468</v>
+      </c>
       <c r="C208" s="8" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E208" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="209" ht="18" spans="1:5">
-      <c r="A209" s="12"/>
-      <c r="B209" s="7" t="s">
-        <v>470</v>
-      </c>
+      <c r="A209" s="10"/>
+      <c r="B209" s="10"/>
       <c r="C209" s="8" t="s">
         <v>471</v>
       </c>
@@ -6116,7 +6076,7 @@
       </c>
     </row>
     <row r="210" ht="18" spans="1:5">
-      <c r="A210" s="12"/>
+      <c r="A210" s="10"/>
       <c r="B210" s="10"/>
       <c r="C210" s="8" t="s">
         <v>473</v>
@@ -6129,7 +6089,7 @@
       </c>
     </row>
     <row r="211" ht="18" spans="1:5">
-      <c r="A211" s="12"/>
+      <c r="A211" s="10"/>
       <c r="B211" s="10"/>
       <c r="C211" s="8" t="s">
         <v>475</v>
@@ -6142,7 +6102,7 @@
       </c>
     </row>
     <row r="212" ht="18" spans="1:5">
-      <c r="A212" s="12"/>
+      <c r="A212" s="10"/>
       <c r="B212" s="10"/>
       <c r="C212" s="8" t="s">
         <v>477</v>
@@ -6155,7 +6115,7 @@
       </c>
     </row>
     <row r="213" ht="18" spans="1:5">
-      <c r="A213" s="12"/>
+      <c r="A213" s="10"/>
       <c r="B213" s="10"/>
       <c r="C213" s="8" t="s">
         <v>479</v>
@@ -6168,7 +6128,7 @@
       </c>
     </row>
     <row r="214" ht="18" spans="1:5">
-      <c r="A214" s="12"/>
+      <c r="A214" s="10"/>
       <c r="B214" s="10"/>
       <c r="C214" s="8" t="s">
         <v>481</v>
@@ -6181,8 +6141,8 @@
       </c>
     </row>
     <row r="215" ht="18" spans="1:5">
-      <c r="A215" s="12"/>
-      <c r="B215" s="10"/>
+      <c r="A215" s="10"/>
+      <c r="B215" s="11"/>
       <c r="C215" s="8" t="s">
         <v>483</v>
       </c>
@@ -6194,23 +6154,23 @@
       </c>
     </row>
     <row r="216" ht="18" spans="1:5">
-      <c r="A216" s="12"/>
-      <c r="B216" s="11"/>
+      <c r="A216" s="10"/>
+      <c r="B216" s="7" t="s">
+        <v>485</v>
+      </c>
       <c r="C216" s="8" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E216" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="217" ht="18" spans="1:5">
-      <c r="A217" s="12"/>
-      <c r="B217" s="7" t="s">
-        <v>487</v>
-      </c>
+      <c r="A217" s="10"/>
+      <c r="B217" s="10"/>
       <c r="C217" s="8" t="s">
         <v>488</v>
       </c>
@@ -6222,7 +6182,7 @@
       </c>
     </row>
     <row r="218" ht="18" spans="1:5">
-      <c r="A218" s="12"/>
+      <c r="A218" s="10"/>
       <c r="B218" s="10"/>
       <c r="C218" s="8" t="s">
         <v>490</v>
@@ -6235,7 +6195,7 @@
       </c>
     </row>
     <row r="219" ht="18" spans="1:5">
-      <c r="A219" s="12"/>
+      <c r="A219" s="10"/>
       <c r="B219" s="10"/>
       <c r="C219" s="8" t="s">
         <v>492</v>
@@ -6248,7 +6208,7 @@
       </c>
     </row>
     <row r="220" ht="18" spans="1:5">
-      <c r="A220" s="12"/>
+      <c r="A220" s="10"/>
       <c r="B220" s="10"/>
       <c r="C220" s="8" t="s">
         <v>494</v>
@@ -6261,7 +6221,7 @@
       </c>
     </row>
     <row r="221" ht="18" spans="1:5">
-      <c r="A221" s="12"/>
+      <c r="A221" s="10"/>
       <c r="B221" s="10"/>
       <c r="C221" s="8" t="s">
         <v>496</v>
@@ -6274,7 +6234,7 @@
       </c>
     </row>
     <row r="222" ht="18" spans="1:5">
-      <c r="A222" s="12"/>
+      <c r="A222" s="10"/>
       <c r="B222" s="10"/>
       <c r="C222" s="8" t="s">
         <v>498</v>
@@ -6287,8 +6247,8 @@
       </c>
     </row>
     <row r="223" ht="18" spans="1:5">
-      <c r="A223" s="12"/>
-      <c r="B223" s="10"/>
+      <c r="A223" s="10"/>
+      <c r="B223" s="11"/>
       <c r="C223" s="8" t="s">
         <v>500</v>
       </c>
@@ -6300,23 +6260,23 @@
       </c>
     </row>
     <row r="224" ht="18" spans="1:5">
-      <c r="A224" s="12"/>
-      <c r="B224" s="11"/>
+      <c r="A224" s="10"/>
+      <c r="B224" s="7" t="s">
+        <v>502</v>
+      </c>
       <c r="C224" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E224" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="225" ht="18" spans="1:5">
-      <c r="A225" s="12"/>
-      <c r="B225" s="7" t="s">
-        <v>504</v>
-      </c>
+      <c r="A225" s="10"/>
+      <c r="B225" s="10"/>
       <c r="C225" s="8" t="s">
         <v>505</v>
       </c>
@@ -6328,7 +6288,7 @@
       </c>
     </row>
     <row r="226" ht="18" spans="1:5">
-      <c r="A226" s="12"/>
+      <c r="A226" s="10"/>
       <c r="B226" s="10"/>
       <c r="C226" s="8" t="s">
         <v>507</v>
@@ -6341,7 +6301,7 @@
       </c>
     </row>
     <row r="227" ht="18" spans="1:5">
-      <c r="A227" s="12"/>
+      <c r="A227" s="10"/>
       <c r="B227" s="10"/>
       <c r="C227" s="8" t="s">
         <v>509</v>
@@ -6354,7 +6314,7 @@
       </c>
     </row>
     <row r="228" ht="18" spans="1:5">
-      <c r="A228" s="12"/>
+      <c r="A228" s="10"/>
       <c r="B228" s="10"/>
       <c r="C228" s="8" t="s">
         <v>511</v>
@@ -6367,7 +6327,7 @@
       </c>
     </row>
     <row r="229" ht="18" spans="1:5">
-      <c r="A229" s="12"/>
+      <c r="A229" s="10"/>
       <c r="B229" s="10"/>
       <c r="C229" s="8" t="s">
         <v>513</v>
@@ -6380,7 +6340,7 @@
       </c>
     </row>
     <row r="230" ht="18" spans="1:5">
-      <c r="A230" s="12"/>
+      <c r="A230" s="10"/>
       <c r="B230" s="10"/>
       <c r="C230" s="8" t="s">
         <v>515</v>
@@ -6393,8 +6353,8 @@
       </c>
     </row>
     <row r="231" ht="18" spans="1:5">
-      <c r="A231" s="12"/>
-      <c r="B231" s="10"/>
+      <c r="A231" s="10"/>
+      <c r="B231" s="11"/>
       <c r="C231" s="8" t="s">
         <v>517</v>
       </c>
@@ -6406,23 +6366,23 @@
       </c>
     </row>
     <row r="232" ht="18" spans="1:5">
-      <c r="A232" s="12"/>
-      <c r="B232" s="11"/>
+      <c r="A232" s="10"/>
+      <c r="B232" s="7" t="s">
+        <v>519</v>
+      </c>
       <c r="C232" s="8" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E232" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="233" ht="18" spans="1:5">
-      <c r="A233" s="12"/>
-      <c r="B233" s="7" t="s">
-        <v>521</v>
-      </c>
+      <c r="A233" s="10"/>
+      <c r="B233" s="10"/>
       <c r="C233" s="8" t="s">
         <v>522</v>
       </c>
@@ -6434,7 +6394,7 @@
       </c>
     </row>
     <row r="234" ht="18" spans="1:5">
-      <c r="A234" s="12"/>
+      <c r="A234" s="10"/>
       <c r="B234" s="10"/>
       <c r="C234" s="8" t="s">
         <v>524</v>
@@ -6447,8 +6407,8 @@
       </c>
     </row>
     <row r="235" ht="18" spans="1:5">
-      <c r="A235" s="12"/>
-      <c r="B235" s="10"/>
+      <c r="A235" s="10"/>
+      <c r="B235" s="11"/>
       <c r="C235" s="8" t="s">
         <v>526</v>
       </c>
@@ -6460,23 +6420,23 @@
       </c>
     </row>
     <row r="236" ht="18" spans="1:5">
-      <c r="A236" s="12"/>
-      <c r="B236" s="11"/>
+      <c r="A236" s="10"/>
+      <c r="B236" s="7" t="s">
+        <v>528</v>
+      </c>
       <c r="C236" s="8" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E236" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="237" ht="18" spans="1:5">
-      <c r="A237" s="12"/>
-      <c r="B237" s="7" t="s">
-        <v>530</v>
-      </c>
+      <c r="A237" s="10"/>
+      <c r="B237" s="10"/>
       <c r="C237" s="8" t="s">
         <v>531</v>
       </c>
@@ -6488,7 +6448,7 @@
       </c>
     </row>
     <row r="238" ht="18" spans="1:5">
-      <c r="A238" s="12"/>
+      <c r="A238" s="10"/>
       <c r="B238" s="10"/>
       <c r="C238" s="8" t="s">
         <v>533</v>
@@ -6501,7 +6461,7 @@
       </c>
     </row>
     <row r="239" ht="18" spans="1:5">
-      <c r="A239" s="12"/>
+      <c r="A239" s="10"/>
       <c r="B239" s="10"/>
       <c r="C239" s="8" t="s">
         <v>535</v>
@@ -6514,8 +6474,8 @@
       </c>
     </row>
     <row r="240" ht="18" spans="1:5">
-      <c r="A240" s="12"/>
-      <c r="B240" s="10"/>
+      <c r="A240" s="10"/>
+      <c r="B240" s="11"/>
       <c r="C240" s="8" t="s">
         <v>537</v>
       </c>
@@ -6527,23 +6487,23 @@
       </c>
     </row>
     <row r="241" ht="18" spans="1:5">
-      <c r="A241" s="12"/>
-      <c r="B241" s="11"/>
+      <c r="A241" s="10"/>
+      <c r="B241" s="7" t="s">
+        <v>539</v>
+      </c>
       <c r="C241" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E241" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="242" ht="18" spans="1:5">
-      <c r="A242" s="12"/>
-      <c r="B242" s="7" t="s">
-        <v>541</v>
-      </c>
+      <c r="A242" s="10"/>
+      <c r="B242" s="10"/>
       <c r="C242" s="8" t="s">
         <v>542</v>
       </c>
@@ -6555,7 +6515,7 @@
       </c>
     </row>
     <row r="243" ht="18" spans="1:5">
-      <c r="A243" s="12"/>
+      <c r="A243" s="10"/>
       <c r="B243" s="10"/>
       <c r="C243" s="8" t="s">
         <v>544</v>
@@ -6568,7 +6528,7 @@
       </c>
     </row>
     <row r="244" ht="18" spans="1:5">
-      <c r="A244" s="12"/>
+      <c r="A244" s="10"/>
       <c r="B244" s="10"/>
       <c r="C244" s="8" t="s">
         <v>546</v>
@@ -6581,8 +6541,8 @@
       </c>
     </row>
     <row r="245" ht="18" spans="1:5">
-      <c r="A245" s="12"/>
-      <c r="B245" s="10"/>
+      <c r="A245" s="10"/>
+      <c r="B245" s="11"/>
       <c r="C245" s="8" t="s">
         <v>548</v>
       </c>
@@ -6594,23 +6554,23 @@
       </c>
     </row>
     <row r="246" ht="18" spans="1:5">
-      <c r="A246" s="12"/>
-      <c r="B246" s="11"/>
+      <c r="A246" s="10"/>
+      <c r="B246" s="7" t="s">
+        <v>550</v>
+      </c>
       <c r="C246" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E246" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="247" ht="18" spans="1:5">
-      <c r="A247" s="12"/>
-      <c r="B247" s="7" t="s">
-        <v>552</v>
-      </c>
+      <c r="A247" s="10"/>
+      <c r="B247" s="10"/>
       <c r="C247" s="8" t="s">
         <v>553</v>
       </c>
@@ -6622,7 +6582,7 @@
       </c>
     </row>
     <row r="248" ht="18" spans="1:5">
-      <c r="A248" s="12"/>
+      <c r="A248" s="10"/>
       <c r="B248" s="10"/>
       <c r="C248" s="8" t="s">
         <v>555</v>
@@ -6635,7 +6595,7 @@
       </c>
     </row>
     <row r="249" ht="18" spans="1:5">
-      <c r="A249" s="12"/>
+      <c r="A249" s="10"/>
       <c r="B249" s="10"/>
       <c r="C249" s="8" t="s">
         <v>557</v>
@@ -6648,8 +6608,8 @@
       </c>
     </row>
     <row r="250" ht="18" spans="1:5">
-      <c r="A250" s="12"/>
-      <c r="B250" s="10"/>
+      <c r="A250" s="10"/>
+      <c r="B250" s="11"/>
       <c r="C250" s="8" t="s">
         <v>559</v>
       </c>
@@ -6661,23 +6621,23 @@
       </c>
     </row>
     <row r="251" ht="18" spans="1:5">
-      <c r="A251" s="12"/>
-      <c r="B251" s="11"/>
+      <c r="A251" s="10"/>
+      <c r="B251" s="7" t="s">
+        <v>561</v>
+      </c>
       <c r="C251" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="252" ht="18" spans="1:5">
-      <c r="A252" s="12"/>
-      <c r="B252" s="7" t="s">
-        <v>563</v>
-      </c>
+      <c r="A252" s="10"/>
+      <c r="B252" s="10"/>
       <c r="C252" s="8" t="s">
         <v>564</v>
       </c>
@@ -6688,8 +6648,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" ht="36" spans="1:5">
-      <c r="A253" s="12"/>
+    <row r="253" ht="18" spans="1:5">
+      <c r="A253" s="10"/>
       <c r="B253" s="10"/>
       <c r="C253" s="8" t="s">
         <v>566</v>
@@ -6702,7 +6662,7 @@
       </c>
     </row>
     <row r="254" ht="18" spans="1:5">
-      <c r="A254" s="12"/>
+      <c r="A254" s="10"/>
       <c r="B254" s="10"/>
       <c r="C254" s="8" t="s">
         <v>568</v>
@@ -6715,7 +6675,7 @@
       </c>
     </row>
     <row r="255" ht="18" spans="1:5">
-      <c r="A255" s="12"/>
+      <c r="A255" s="10"/>
       <c r="B255" s="10"/>
       <c r="C255" s="8" t="s">
         <v>570</v>
@@ -6728,7 +6688,7 @@
       </c>
     </row>
     <row r="256" ht="18" spans="1:5">
-      <c r="A256" s="12"/>
+      <c r="A256" s="10"/>
       <c r="B256" s="10"/>
       <c r="C256" s="8" t="s">
         <v>572</v>
@@ -6741,7 +6701,7 @@
       </c>
     </row>
     <row r="257" ht="18" spans="1:5">
-      <c r="A257" s="12"/>
+      <c r="A257" s="10"/>
       <c r="B257" s="10"/>
       <c r="C257" s="8" t="s">
         <v>574</v>
@@ -6754,7 +6714,7 @@
       </c>
     </row>
     <row r="258" ht="18" spans="1:5">
-      <c r="A258" s="12"/>
+      <c r="A258" s="10"/>
       <c r="B258" s="10"/>
       <c r="C258" s="8" t="s">
         <v>576</v>
@@ -6766,9 +6726,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" ht="36" spans="1:5">
-      <c r="A259" s="12"/>
-      <c r="B259" s="10"/>
+    <row r="259" ht="18" spans="1:5">
+      <c r="A259" s="10"/>
+      <c r="B259" s="11"/>
       <c r="C259" s="8" t="s">
         <v>578</v>
       </c>
@@ -6780,23 +6740,23 @@
       </c>
     </row>
     <row r="260" ht="18" spans="1:5">
-      <c r="A260" s="12"/>
-      <c r="B260" s="11"/>
+      <c r="A260" s="10"/>
+      <c r="B260" s="7" t="s">
+        <v>580</v>
+      </c>
       <c r="C260" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D260" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E260" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="261" ht="18" spans="1:5">
-      <c r="A261" s="12"/>
-      <c r="B261" s="7" t="s">
-        <v>582</v>
-      </c>
+      <c r="A261" s="10"/>
+      <c r="B261" s="10"/>
       <c r="C261" s="8" t="s">
         <v>583</v>
       </c>
@@ -6808,23 +6768,23 @@
       </c>
     </row>
     <row r="262" ht="18" spans="1:5">
-      <c r="A262" s="12"/>
+      <c r="A262" s="10"/>
       <c r="B262" s="10"/>
       <c r="C262" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D262" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="D262" s="8" t="s">
-        <v>586</v>
-      </c>
       <c r="E262" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="263" ht="18" spans="1:5">
-      <c r="A263" s="12"/>
+      <c r="A263" s="10"/>
       <c r="B263" s="10"/>
       <c r="C263" s="8" t="s">
-        <v>158</v>
+        <v>586</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>587</v>
@@ -6834,7 +6794,7 @@
       </c>
     </row>
     <row r="264" ht="18" spans="1:5">
-      <c r="A264" s="12"/>
+      <c r="A264" s="10"/>
       <c r="B264" s="10"/>
       <c r="C264" s="8" t="s">
         <v>588</v>
@@ -6847,8 +6807,8 @@
       </c>
     </row>
     <row r="265" ht="18" spans="1:5">
-      <c r="A265" s="12"/>
-      <c r="B265" s="10"/>
+      <c r="A265" s="10"/>
+      <c r="B265" s="11"/>
       <c r="C265" s="8" t="s">
         <v>590</v>
       </c>
@@ -6860,23 +6820,23 @@
       </c>
     </row>
     <row r="266" ht="18" spans="1:5">
-      <c r="A266" s="12"/>
-      <c r="B266" s="11"/>
+      <c r="A266" s="10"/>
+      <c r="B266" s="7" t="s">
+        <v>592</v>
+      </c>
       <c r="C266" s="8" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E266" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="267" ht="18" spans="1:5">
-      <c r="A267" s="12"/>
-      <c r="B267" s="7" t="s">
-        <v>594</v>
-      </c>
+      <c r="A267" s="10"/>
+      <c r="B267" s="10"/>
       <c r="C267" s="8" t="s">
         <v>595</v>
       </c>
@@ -6888,7 +6848,7 @@
       </c>
     </row>
     <row r="268" ht="18" spans="1:5">
-      <c r="A268" s="12"/>
+      <c r="A268" s="10"/>
       <c r="B268" s="10"/>
       <c r="C268" s="8" t="s">
         <v>597</v>
@@ -6901,7 +6861,7 @@
       </c>
     </row>
     <row r="269" ht="18" spans="1:5">
-      <c r="A269" s="12"/>
+      <c r="A269" s="10"/>
       <c r="B269" s="10"/>
       <c r="C269" s="8" t="s">
         <v>599</v>
@@ -6914,7 +6874,7 @@
       </c>
     </row>
     <row r="270" ht="18" spans="1:5">
-      <c r="A270" s="12"/>
+      <c r="A270" s="10"/>
       <c r="B270" s="10"/>
       <c r="C270" s="8" t="s">
         <v>601</v>
@@ -6927,8 +6887,8 @@
       </c>
     </row>
     <row r="271" ht="18" spans="1:5">
-      <c r="A271" s="12"/>
-      <c r="B271" s="10"/>
+      <c r="A271" s="10"/>
+      <c r="B271" s="11"/>
       <c r="C271" s="8" t="s">
         <v>603</v>
       </c>
@@ -6940,23 +6900,23 @@
       </c>
     </row>
     <row r="272" ht="18" spans="1:5">
-      <c r="A272" s="12"/>
-      <c r="B272" s="11"/>
+      <c r="A272" s="10"/>
+      <c r="B272" s="7" t="s">
+        <v>605</v>
+      </c>
       <c r="C272" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E272" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="273" ht="18" spans="1:5">
-      <c r="A273" s="12"/>
-      <c r="B273" s="7" t="s">
-        <v>607</v>
-      </c>
+      <c r="A273" s="10"/>
+      <c r="B273" s="10"/>
       <c r="C273" s="8" t="s">
         <v>608</v>
       </c>
@@ -6968,7 +6928,7 @@
       </c>
     </row>
     <row r="274" ht="18" spans="1:5">
-      <c r="A274" s="12"/>
+      <c r="A274" s="10"/>
       <c r="B274" s="10"/>
       <c r="C274" s="8" t="s">
         <v>610</v>
@@ -6981,8 +6941,8 @@
       </c>
     </row>
     <row r="275" ht="18" spans="1:5">
-      <c r="A275" s="12"/>
-      <c r="B275" s="10"/>
+      <c r="A275" s="10"/>
+      <c r="B275" s="11"/>
       <c r="C275" s="8" t="s">
         <v>612</v>
       </c>
@@ -6994,23 +6954,23 @@
       </c>
     </row>
     <row r="276" ht="18" spans="1:5">
-      <c r="A276" s="12"/>
-      <c r="B276" s="11"/>
+      <c r="A276" s="10"/>
+      <c r="B276" s="7" t="s">
+        <v>614</v>
+      </c>
       <c r="C276" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E276" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="277" ht="18" spans="1:5">
-      <c r="A277" s="12"/>
-      <c r="B277" s="7" t="s">
-        <v>616</v>
-      </c>
+      <c r="A277" s="10"/>
+      <c r="B277" s="10"/>
       <c r="C277" s="8" t="s">
         <v>617</v>
       </c>
@@ -7021,8 +6981,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="278" ht="18" spans="1:5">
-      <c r="A278" s="12"/>
+    <row r="278" ht="53" spans="1:5">
+      <c r="A278" s="10"/>
       <c r="B278" s="10"/>
       <c r="C278" s="8" t="s">
         <v>619</v>
@@ -7034,8 +6994,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="279" ht="53" spans="1:5">
-      <c r="A279" s="12"/>
+    <row r="279" ht="18" spans="1:5">
+      <c r="A279" s="10"/>
       <c r="B279" s="10"/>
       <c r="C279" s="8" t="s">
         <v>621</v>
@@ -7048,7 +7008,7 @@
       </c>
     </row>
     <row r="280" ht="18" spans="1:5">
-      <c r="A280" s="12"/>
+      <c r="A280" s="10"/>
       <c r="B280" s="10"/>
       <c r="C280" s="8" t="s">
         <v>623</v>
@@ -7061,7 +7021,7 @@
       </c>
     </row>
     <row r="281" ht="18" spans="1:5">
-      <c r="A281" s="12"/>
+      <c r="A281" s="10"/>
       <c r="B281" s="10"/>
       <c r="C281" s="8" t="s">
         <v>625</v>
@@ -7074,8 +7034,8 @@
       </c>
     </row>
     <row r="282" ht="18" spans="1:5">
-      <c r="A282" s="12"/>
-      <c r="B282" s="10"/>
+      <c r="A282" s="10"/>
+      <c r="B282" s="11"/>
       <c r="C282" s="8" t="s">
         <v>627</v>
       </c>
@@ -7087,23 +7047,23 @@
       </c>
     </row>
     <row r="283" ht="18" spans="1:5">
-      <c r="A283" s="12"/>
-      <c r="B283" s="11"/>
+      <c r="A283" s="10"/>
+      <c r="B283" s="7" t="s">
+        <v>629</v>
+      </c>
       <c r="C283" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E283" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="284" ht="18" spans="1:5">
-      <c r="A284" s="12"/>
-      <c r="B284" s="7" t="s">
-        <v>631</v>
-      </c>
+      <c r="A284" s="10"/>
+      <c r="B284" s="10"/>
       <c r="C284" s="8" t="s">
         <v>632</v>
       </c>
@@ -7115,7 +7075,7 @@
       </c>
     </row>
     <row r="285" ht="18" spans="1:5">
-      <c r="A285" s="12"/>
+      <c r="A285" s="10"/>
       <c r="B285" s="10"/>
       <c r="C285" s="8" t="s">
         <v>634</v>
@@ -7128,7 +7088,7 @@
       </c>
     </row>
     <row r="286" ht="18" spans="1:5">
-      <c r="A286" s="12"/>
+      <c r="A286" s="10"/>
       <c r="B286" s="10"/>
       <c r="C286" s="8" t="s">
         <v>636</v>
@@ -7140,8 +7100,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="287" ht="18" spans="1:5">
-      <c r="A287" s="12"/>
+    <row r="287" ht="36" spans="1:5">
+      <c r="A287" s="10"/>
       <c r="B287" s="10"/>
       <c r="C287" s="8" t="s">
         <v>638</v>
@@ -7153,9 +7113,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="288" ht="36" spans="1:5">
-      <c r="A288" s="12"/>
-      <c r="B288" s="10"/>
+    <row r="288" ht="18" spans="1:5">
+      <c r="A288" s="10"/>
+      <c r="B288" s="11"/>
       <c r="C288" s="8" t="s">
         <v>640</v>
       </c>
@@ -7167,23 +7127,23 @@
       </c>
     </row>
     <row r="289" ht="18" spans="1:5">
-      <c r="A289" s="12"/>
-      <c r="B289" s="11"/>
+      <c r="A289" s="10"/>
+      <c r="B289" s="7" t="s">
+        <v>642</v>
+      </c>
       <c r="C289" s="8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E289" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="290" ht="18" spans="1:5">
-      <c r="A290" s="12"/>
-      <c r="B290" s="7" t="s">
-        <v>644</v>
-      </c>
+      <c r="A290" s="10"/>
+      <c r="B290" s="10"/>
       <c r="C290" s="8" t="s">
         <v>645</v>
       </c>
@@ -7195,8 +7155,8 @@
       </c>
     </row>
     <row r="291" ht="18" spans="1:5">
-      <c r="A291" s="12"/>
-      <c r="B291" s="10"/>
+      <c r="A291" s="10"/>
+      <c r="B291" s="11"/>
       <c r="C291" s="8" t="s">
         <v>647</v>
       </c>
@@ -7208,23 +7168,23 @@
       </c>
     </row>
     <row r="292" ht="18" spans="1:5">
-      <c r="A292" s="12"/>
-      <c r="B292" s="11"/>
-      <c r="C292" s="8" t="s">
+      <c r="A292" s="10"/>
+      <c r="B292" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="D292" s="8" t="s">
+      <c r="C292" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="E292" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="293" ht="36" spans="1:5">
-      <c r="A293" s="12"/>
-      <c r="B293" s="2" t="s">
+      <c r="D292" s="3" t="s">
         <v>651</v>
       </c>
+      <c r="E292" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="293" ht="18" spans="1:5">
+      <c r="A293" s="10"/>
+      <c r="B293" s="5"/>
       <c r="C293" s="3" t="s">
         <v>652</v>
       </c>
@@ -7236,8 +7196,8 @@
       </c>
     </row>
     <row r="294" ht="18" spans="1:5">
-      <c r="A294" s="12"/>
-      <c r="B294" s="5"/>
+      <c r="A294" s="10"/>
+      <c r="B294" s="6"/>
       <c r="C294" s="3" t="s">
         <v>654</v>
       </c>
@@ -7249,23 +7209,23 @@
       </c>
     </row>
     <row r="295" ht="18" spans="1:5">
-      <c r="A295" s="12"/>
-      <c r="B295" s="6"/>
+      <c r="A295" s="10"/>
+      <c r="B295" s="2" t="s">
+        <v>656</v>
+      </c>
       <c r="C295" s="3" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="296" ht="18" spans="1:5">
-      <c r="A296" s="12"/>
-      <c r="B296" s="2" t="s">
-        <v>658</v>
-      </c>
+      <c r="A296" s="10"/>
+      <c r="B296" s="5"/>
       <c r="C296" s="3" t="s">
         <v>659</v>
       </c>
@@ -7277,8 +7237,8 @@
       </c>
     </row>
     <row r="297" ht="18" spans="1:5">
-      <c r="A297" s="12"/>
-      <c r="B297" s="5"/>
+      <c r="A297" s="10"/>
+      <c r="B297" s="6"/>
       <c r="C297" s="3" t="s">
         <v>661</v>
       </c>
@@ -7290,23 +7250,23 @@
       </c>
     </row>
     <row r="298" ht="18" spans="1:5">
-      <c r="A298" s="12"/>
-      <c r="B298" s="6"/>
+      <c r="A298" s="10"/>
+      <c r="B298" s="2" t="s">
+        <v>663</v>
+      </c>
       <c r="C298" s="3" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E298" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="299" ht="18" spans="1:5">
-      <c r="A299" s="12"/>
-      <c r="B299" s="2" t="s">
-        <v>665</v>
-      </c>
+      <c r="A299" s="10"/>
+      <c r="B299" s="5"/>
       <c r="C299" s="3" t="s">
         <v>666</v>
       </c>
@@ -7318,8 +7278,8 @@
       </c>
     </row>
     <row r="300" ht="18" spans="1:5">
-      <c r="A300" s="12"/>
-      <c r="B300" s="5"/>
+      <c r="A300" s="10"/>
+      <c r="B300" s="6"/>
       <c r="C300" s="3" t="s">
         <v>668</v>
       </c>
@@ -7330,24 +7290,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="301" ht="36" spans="1:5">
-      <c r="A301" s="12"/>
-      <c r="B301" s="6"/>
+    <row r="301" ht="18" spans="1:5">
+      <c r="A301" s="10"/>
+      <c r="B301" s="2" t="s">
+        <v>670</v>
+      </c>
       <c r="C301" s="3" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E301" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="302" ht="18" spans="1:5">
-      <c r="A302" s="12"/>
-      <c r="B302" s="2" t="s">
-        <v>672</v>
-      </c>
+      <c r="A302" s="10"/>
+      <c r="B302" s="5"/>
       <c r="C302" s="3" t="s">
         <v>673</v>
       </c>
@@ -7359,7 +7319,7 @@
       </c>
     </row>
     <row r="303" ht="18" spans="1:5">
-      <c r="A303" s="12"/>
+      <c r="A303" s="10"/>
       <c r="B303" s="5"/>
       <c r="C303" s="3" t="s">
         <v>675</v>
@@ -7371,8 +7331,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="304" ht="18" spans="1:5">
-      <c r="A304" s="12"/>
+    <row r="304" ht="36" spans="1:5">
+      <c r="A304" s="10"/>
       <c r="B304" s="5"/>
       <c r="C304" s="3" t="s">
         <v>677</v>
@@ -7384,9 +7344,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="305" ht="36" spans="1:5">
-      <c r="A305" s="12"/>
-      <c r="B305" s="5"/>
+    <row r="305" ht="18" spans="1:5">
+      <c r="A305" s="10"/>
+      <c r="B305" s="6"/>
       <c r="C305" s="3" t="s">
         <v>679</v>
       </c>
@@ -7399,22 +7359,22 @@
     </row>
     <row r="306" ht="18" spans="1:5">
       <c r="A306" s="12"/>
-      <c r="B306" s="6"/>
+      <c r="B306" s="2" t="s">
+        <v>681</v>
+      </c>
       <c r="C306" s="3" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E306" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="307" ht="36" spans="1:5">
-      <c r="A307" s="13"/>
-      <c r="B307" s="2" t="s">
-        <v>683</v>
-      </c>
+    <row r="307" ht="53" spans="1:5">
+      <c r="A307" s="12"/>
+      <c r="B307" s="5"/>
       <c r="C307" s="3" t="s">
         <v>684</v>
       </c>
@@ -7425,8 +7385,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="308" ht="53" spans="1:5">
-      <c r="A308" s="13"/>
+    <row r="308" ht="36" spans="1:5">
+      <c r="A308" s="12"/>
       <c r="B308" s="5"/>
       <c r="C308" s="3" t="s">
         <v>686</v>
@@ -7438,8 +7398,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" ht="36" spans="1:5">
-      <c r="A309" s="13"/>
+    <row r="309" ht="18" spans="1:5">
+      <c r="A309" s="12"/>
       <c r="B309" s="5"/>
       <c r="C309" s="3" t="s">
         <v>688</v>
@@ -7451,8 +7411,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="310" ht="18" spans="1:5">
-      <c r="A310" s="13"/>
+    <row r="310" ht="36" spans="1:5">
+      <c r="A310" s="12"/>
       <c r="B310" s="5"/>
       <c r="C310" s="3" t="s">
         <v>690</v>
@@ -7465,7 +7425,7 @@
       </c>
     </row>
     <row r="311" ht="36" spans="1:5">
-      <c r="A311" s="13"/>
+      <c r="A311" s="12"/>
       <c r="B311" s="5"/>
       <c r="C311" s="3" t="s">
         <v>692</v>
@@ -7477,8 +7437,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312" ht="36" spans="1:5">
-      <c r="A312" s="13"/>
+    <row r="312" ht="18" spans="1:5">
+      <c r="A312" s="12"/>
       <c r="B312" s="5"/>
       <c r="C312" s="3" t="s">
         <v>694</v>
@@ -7490,8 +7450,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313" ht="18" spans="1:5">
-      <c r="A313" s="13"/>
+    <row r="313" ht="36" spans="1:5">
+      <c r="A313" s="12"/>
       <c r="B313" s="5"/>
       <c r="C313" s="3" t="s">
         <v>696</v>
@@ -7504,8 +7464,8 @@
       </c>
     </row>
     <row r="314" ht="36" spans="1:5">
-      <c r="A314" s="13"/>
-      <c r="B314" s="5"/>
+      <c r="A314" s="12"/>
+      <c r="B314" s="6"/>
       <c r="C314" s="3" t="s">
         <v>698</v>
       </c>
@@ -7516,26 +7476,26 @@
         <v>9</v>
       </c>
     </row>
-    <row r="315" ht="36" spans="1:5">
-      <c r="A315" s="13"/>
-      <c r="B315" s="6"/>
+    <row r="315" ht="18" spans="1:5">
+      <c r="A315" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>701</v>
+      </c>
       <c r="C315" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E315" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="316" ht="18" spans="1:5">
-      <c r="A316" s="14" t="s">
-        <v>702</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>703</v>
-      </c>
+      <c r="A316" s="5"/>
+      <c r="B316" s="5"/>
       <c r="C316" s="3" t="s">
         <v>704</v>
       </c>
@@ -7547,7 +7507,7 @@
       </c>
     </row>
     <row r="317" ht="18" spans="1:5">
-      <c r="A317" s="14"/>
+      <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="3" t="s">
         <v>706</v>
@@ -7560,7 +7520,7 @@
       </c>
     </row>
     <row r="318" ht="36" spans="1:5">
-      <c r="A318" s="14"/>
+      <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="3" t="s">
         <v>708</v>
@@ -7572,123 +7532,84 @@
         <v>9</v>
       </c>
     </row>
-    <row r="319" ht="36" spans="1:5">
-      <c r="A319" s="14"/>
-      <c r="B319" s="5"/>
-      <c r="C319" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="D319" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="E319" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="320" ht="36" spans="1:5">
-      <c r="A320" s="14"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="D320" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="E320" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="321" ht="18" spans="1:5">
-      <c r="A321" s="15"/>
-      <c r="B321" s="6"/>
-      <c r="C321" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="E321" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E321" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E318" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <mergeCells count="73">
-    <mergeCell ref="A2:A98"/>
-    <mergeCell ref="A99:A116"/>
-    <mergeCell ref="A117:A155"/>
-    <mergeCell ref="A156:A186"/>
-    <mergeCell ref="A187:A200"/>
-    <mergeCell ref="A201:A306"/>
-    <mergeCell ref="A316:A321"/>
+    <mergeCell ref="A2:A97"/>
+    <mergeCell ref="A98:A115"/>
+    <mergeCell ref="A116:A154"/>
+    <mergeCell ref="A155:A185"/>
+    <mergeCell ref="A186:A199"/>
+    <mergeCell ref="A200:A305"/>
+    <mergeCell ref="A315:A318"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="B13:B20"/>
-    <mergeCell ref="B21:B28"/>
-    <mergeCell ref="B29:B37"/>
-    <mergeCell ref="B38:B46"/>
-    <mergeCell ref="B47:B54"/>
-    <mergeCell ref="B55:B60"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="B66:B74"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="B84:B87"/>
-    <mergeCell ref="B88:B92"/>
-    <mergeCell ref="B93:B98"/>
-    <mergeCell ref="B99:B103"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B111:B112"/>
-    <mergeCell ref="B113:B114"/>
-    <mergeCell ref="B115:B116"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="B126:B130"/>
-    <mergeCell ref="B131:B134"/>
-    <mergeCell ref="B135:B138"/>
-    <mergeCell ref="B139:B145"/>
-    <mergeCell ref="B146:B150"/>
-    <mergeCell ref="B151:B152"/>
-    <mergeCell ref="B153:B155"/>
-    <mergeCell ref="B156:B159"/>
-    <mergeCell ref="B160:B164"/>
-    <mergeCell ref="B165:B167"/>
-    <mergeCell ref="B168:B171"/>
-    <mergeCell ref="B172:B174"/>
-    <mergeCell ref="B175:B177"/>
-    <mergeCell ref="B178:B180"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="B183:B184"/>
-    <mergeCell ref="B185:B186"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="B189:B191"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="B195:B196"/>
-    <mergeCell ref="B198:B200"/>
-    <mergeCell ref="B201:B203"/>
-    <mergeCell ref="B204:B208"/>
-    <mergeCell ref="B209:B216"/>
-    <mergeCell ref="B217:B224"/>
-    <mergeCell ref="B225:B232"/>
-    <mergeCell ref="B233:B236"/>
-    <mergeCell ref="B237:B241"/>
-    <mergeCell ref="B242:B246"/>
-    <mergeCell ref="B247:B251"/>
-    <mergeCell ref="B252:B260"/>
-    <mergeCell ref="B261:B266"/>
-    <mergeCell ref="B267:B272"/>
-    <mergeCell ref="B273:B276"/>
-    <mergeCell ref="B277:B283"/>
-    <mergeCell ref="B284:B289"/>
-    <mergeCell ref="B290:B292"/>
-    <mergeCell ref="B293:B295"/>
-    <mergeCell ref="B296:B298"/>
-    <mergeCell ref="B299:B301"/>
-    <mergeCell ref="B302:B306"/>
-    <mergeCell ref="B307:B315"/>
-    <mergeCell ref="B316:B321"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="B28:B36"/>
+    <mergeCell ref="B37:B45"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="B54:B59"/>
+    <mergeCell ref="B60:B64"/>
+    <mergeCell ref="B65:B73"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="B78:B82"/>
+    <mergeCell ref="B83:B86"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="B92:B97"/>
+    <mergeCell ref="B98:B102"/>
+    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B110:B111"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="B116:B120"/>
+    <mergeCell ref="B121:B124"/>
+    <mergeCell ref="B125:B129"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="B138:B144"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="B152:B154"/>
+    <mergeCell ref="B155:B158"/>
+    <mergeCell ref="B159:B163"/>
+    <mergeCell ref="B164:B166"/>
+    <mergeCell ref="B167:B170"/>
+    <mergeCell ref="B171:B173"/>
+    <mergeCell ref="B174:B176"/>
+    <mergeCell ref="B177:B179"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="B188:B190"/>
+    <mergeCell ref="B191:B192"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B197:B199"/>
+    <mergeCell ref="B200:B202"/>
+    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B208:B215"/>
+    <mergeCell ref="B216:B223"/>
+    <mergeCell ref="B224:B231"/>
+    <mergeCell ref="B232:B235"/>
+    <mergeCell ref="B236:B240"/>
+    <mergeCell ref="B241:B245"/>
+    <mergeCell ref="B246:B250"/>
+    <mergeCell ref="B251:B259"/>
+    <mergeCell ref="B260:B265"/>
+    <mergeCell ref="B266:B271"/>
+    <mergeCell ref="B272:B275"/>
+    <mergeCell ref="B276:B282"/>
+    <mergeCell ref="B283:B288"/>
+    <mergeCell ref="B289:B291"/>
+    <mergeCell ref="B292:B294"/>
+    <mergeCell ref="B295:B297"/>
+    <mergeCell ref="B298:B300"/>
+    <mergeCell ref="B301:B305"/>
+    <mergeCell ref="B306:B314"/>
+    <mergeCell ref="B315:B318"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
